--- a/docs/huyvu/sosach/nam2023/BAO_CAO_CONG_NO_2023.xlsx
+++ b/docs/huyvu/sosach/nam2023/BAO_CAO_CONG_NO_2023.xlsx
@@ -11794,10 +11794,10 @@
         <v>177906011</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>100000000</v>
       </c>
       <c r="D3">
-        <v>177906011</v>
+        <v>77906011</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -12200,10 +12200,10 @@
         <v>171990003</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>5100000000</v>
       </c>
       <c r="D32">
-        <v>171990003</v>
+        <v>-4928009997</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -13012,10 +13012,10 @@
         <v>673086051</v>
       </c>
       <c r="C90">
-        <v>5200000000</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>-4526913949</v>
+        <v>673086051</v>
       </c>
     </row>
     <row r="91" spans="1:4">

--- a/docs/huyvu/sosach/nam2023/BAO_CAO_CONG_NO_2023.xlsx
+++ b/docs/huyvu/sosach/nam2023/BAO_CAO_CONG_NO_2023.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="757">
   <si>
     <t>Đối tượng</t>
   </si>
@@ -26,7 +26,7 @@
     <t>ĐÃ THU</t>
   </si>
   <si>
-    <t>BIẾN ĐỘNG</t>
+    <t>DƯ CUỐI KỲ</t>
   </si>
   <si>
     <t>AGRIBANK  CHI NHÁNH THÀNH PHỐ PLEIKU GIA LAI</t>
@@ -1472,9 +1472,6 @@
     <t>KHO BẠC NHÀ NƯỚC GIA LAI</t>
   </si>
   <si>
-    <t>KHÁCH HÀNG CHUNG</t>
-  </si>
-  <si>
     <t>LIÊN ĐOÀN LAO ĐỘNG HUYỆN CHƯ PRÔNG</t>
   </si>
   <si>
@@ -1604,6 +1601,9 @@
     <t>QUỸ TÍN DỤNG NHÂN DÂN TRÀ BÁ</t>
   </si>
   <si>
+    <t>SỐ DƯ ĐẦU KỲ CHUNG</t>
+  </si>
+  <si>
     <t>SỞ CHỈ HUY TIỀN PHƯƠNG QK</t>
   </si>
   <si>
@@ -1985,7 +1985,7 @@
     <t>MUA VÀO</t>
   </si>
   <si>
-    <t>ĐÀ TRẢ</t>
+    <t>ĐÃ TRẢ</t>
   </si>
   <si>
     <t>CHI NHÁNH CÔNG TY CỔ PHẦN HUETRONICS (TỈNH THỪA THIÊN HUẾ)</t>
@@ -9373,13 +9373,13 @@
         <v>485</v>
       </c>
       <c r="B483">
-        <v>0</v>
+        <v>4950000</v>
       </c>
       <c r="C483">
-        <v>1210309689</v>
+        <v>4950000</v>
       </c>
       <c r="D483">
-        <v>-1210309689</v>
+        <v>0</v>
       </c>
     </row>
     <row r="484" spans="1:4">
@@ -9387,10 +9387,10 @@
         <v>486</v>
       </c>
       <c r="B484">
-        <v>4950000</v>
+        <v>15000000</v>
       </c>
       <c r="C484">
-        <v>4950000</v>
+        <v>15000000</v>
       </c>
       <c r="D484">
         <v>0</v>
@@ -9401,10 +9401,10 @@
         <v>487</v>
       </c>
       <c r="B485">
-        <v>15000000</v>
+        <v>14800000</v>
       </c>
       <c r="C485">
-        <v>15000000</v>
+        <v>14800000</v>
       </c>
       <c r="D485">
         <v>0</v>
@@ -9415,10 +9415,10 @@
         <v>488</v>
       </c>
       <c r="B486">
-        <v>14800000</v>
+        <v>14000000</v>
       </c>
       <c r="C486">
-        <v>14800000</v>
+        <v>14000000</v>
       </c>
       <c r="D486">
         <v>0</v>
@@ -9429,10 +9429,10 @@
         <v>489</v>
       </c>
       <c r="B487">
-        <v>14000000</v>
+        <v>18180000</v>
       </c>
       <c r="C487">
-        <v>14000000</v>
+        <v>18180000</v>
       </c>
       <c r="D487">
         <v>0</v>
@@ -9443,10 +9443,10 @@
         <v>490</v>
       </c>
       <c r="B488">
-        <v>18180000</v>
+        <v>178535000</v>
       </c>
       <c r="C488">
-        <v>18180000</v>
+        <v>178535000</v>
       </c>
       <c r="D488">
         <v>0</v>
@@ -9457,10 +9457,10 @@
         <v>491</v>
       </c>
       <c r="B489">
-        <v>178535000</v>
+        <v>21000000</v>
       </c>
       <c r="C489">
-        <v>178535000</v>
+        <v>21000000</v>
       </c>
       <c r="D489">
         <v>0</v>
@@ -9471,10 +9471,10 @@
         <v>492</v>
       </c>
       <c r="B490">
-        <v>21000000</v>
+        <v>3000000</v>
       </c>
       <c r="C490">
-        <v>21000000</v>
+        <v>3000000</v>
       </c>
       <c r="D490">
         <v>0</v>
@@ -9485,10 +9485,10 @@
         <v>493</v>
       </c>
       <c r="B491">
-        <v>3000000</v>
+        <v>3950000</v>
       </c>
       <c r="C491">
-        <v>3000000</v>
+        <v>3950000</v>
       </c>
       <c r="D491">
         <v>0</v>
@@ -9499,10 +9499,10 @@
         <v>494</v>
       </c>
       <c r="B492">
-        <v>3950000</v>
+        <v>145090001</v>
       </c>
       <c r="C492">
-        <v>3950000</v>
+        <v>145090001</v>
       </c>
       <c r="D492">
         <v>0</v>
@@ -9513,10 +9513,10 @@
         <v>495</v>
       </c>
       <c r="B493">
-        <v>145090001</v>
+        <v>370000</v>
       </c>
       <c r="C493">
-        <v>145090001</v>
+        <v>370000</v>
       </c>
       <c r="D493">
         <v>0</v>
@@ -9527,10 +9527,10 @@
         <v>496</v>
       </c>
       <c r="B494">
-        <v>370000</v>
+        <v>1450000</v>
       </c>
       <c r="C494">
-        <v>370000</v>
+        <v>1450000</v>
       </c>
       <c r="D494">
         <v>0</v>
@@ -9541,10 +9541,10 @@
         <v>497</v>
       </c>
       <c r="B495">
-        <v>1450000</v>
+        <v>21500000</v>
       </c>
       <c r="C495">
-        <v>1450000</v>
+        <v>21500000</v>
       </c>
       <c r="D495">
         <v>0</v>
@@ -9555,10 +9555,10 @@
         <v>498</v>
       </c>
       <c r="B496">
-        <v>21500000</v>
+        <v>590000</v>
       </c>
       <c r="C496">
-        <v>21500000</v>
+        <v>590000</v>
       </c>
       <c r="D496">
         <v>0</v>
@@ -9569,10 +9569,10 @@
         <v>499</v>
       </c>
       <c r="B497">
-        <v>590000</v>
+        <v>220000</v>
       </c>
       <c r="C497">
-        <v>590000</v>
+        <v>220000</v>
       </c>
       <c r="D497">
         <v>0</v>
@@ -9583,10 +9583,10 @@
         <v>500</v>
       </c>
       <c r="B498">
-        <v>220000</v>
+        <v>105940000</v>
       </c>
       <c r="C498">
-        <v>220000</v>
+        <v>105940000</v>
       </c>
       <c r="D498">
         <v>0</v>
@@ -9597,10 +9597,10 @@
         <v>501</v>
       </c>
       <c r="B499">
-        <v>105940000</v>
+        <v>3020000</v>
       </c>
       <c r="C499">
-        <v>105940000</v>
+        <v>3020000</v>
       </c>
       <c r="D499">
         <v>0</v>
@@ -9611,10 +9611,10 @@
         <v>502</v>
       </c>
       <c r="B500">
-        <v>3020000</v>
+        <v>490000</v>
       </c>
       <c r="C500">
-        <v>3020000</v>
+        <v>490000</v>
       </c>
       <c r="D500">
         <v>0</v>
@@ -9625,10 +9625,10 @@
         <v>503</v>
       </c>
       <c r="B501">
-        <v>490000</v>
+        <v>1350000</v>
       </c>
       <c r="C501">
-        <v>490000</v>
+        <v>1350000</v>
       </c>
       <c r="D501">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>504</v>
       </c>
       <c r="B502">
-        <v>1350000</v>
+        <v>85385000</v>
       </c>
       <c r="C502">
-        <v>1350000</v>
+        <v>85385000</v>
       </c>
       <c r="D502">
         <v>0</v>
@@ -9653,10 +9653,10 @@
         <v>505</v>
       </c>
       <c r="B503">
-        <v>85385000</v>
+        <v>4090000</v>
       </c>
       <c r="C503">
-        <v>85385000</v>
+        <v>4090000</v>
       </c>
       <c r="D503">
         <v>0</v>
@@ -9667,10 +9667,10 @@
         <v>506</v>
       </c>
       <c r="B504">
-        <v>4090000</v>
+        <v>4010000</v>
       </c>
       <c r="C504">
-        <v>4090000</v>
+        <v>4010000</v>
       </c>
       <c r="D504">
         <v>0</v>
@@ -9681,10 +9681,10 @@
         <v>507</v>
       </c>
       <c r="B505">
-        <v>4010000</v>
+        <v>13000000</v>
       </c>
       <c r="C505">
-        <v>4010000</v>
+        <v>13000000</v>
       </c>
       <c r="D505">
         <v>0</v>
@@ -9695,10 +9695,10 @@
         <v>508</v>
       </c>
       <c r="B506">
-        <v>13000000</v>
+        <v>920000</v>
       </c>
       <c r="C506">
-        <v>13000000</v>
+        <v>920000</v>
       </c>
       <c r="D506">
         <v>0</v>
@@ -9709,10 +9709,10 @@
         <v>509</v>
       </c>
       <c r="B507">
-        <v>920000</v>
+        <v>3080000</v>
       </c>
       <c r="C507">
-        <v>920000</v>
+        <v>3080000</v>
       </c>
       <c r="D507">
         <v>0</v>
@@ -9723,10 +9723,10 @@
         <v>510</v>
       </c>
       <c r="B508">
-        <v>3080000</v>
+        <v>7550000</v>
       </c>
       <c r="C508">
-        <v>3080000</v>
+        <v>7550000</v>
       </c>
       <c r="D508">
         <v>0</v>
@@ -9737,10 +9737,10 @@
         <v>511</v>
       </c>
       <c r="B509">
-        <v>7550000</v>
+        <v>27000000</v>
       </c>
       <c r="C509">
-        <v>7550000</v>
+        <v>27000000</v>
       </c>
       <c r="D509">
         <v>0</v>
@@ -9751,10 +9751,10 @@
         <v>512</v>
       </c>
       <c r="B510">
-        <v>27000000</v>
+        <v>94840000</v>
       </c>
       <c r="C510">
-        <v>27000000</v>
+        <v>94840000</v>
       </c>
       <c r="D510">
         <v>0</v>
@@ -9765,10 +9765,10 @@
         <v>513</v>
       </c>
       <c r="B511">
-        <v>94840000</v>
+        <v>1500000</v>
       </c>
       <c r="C511">
-        <v>94840000</v>
+        <v>1500000</v>
       </c>
       <c r="D511">
         <v>0</v>
@@ -9779,10 +9779,10 @@
         <v>514</v>
       </c>
       <c r="B512">
-        <v>1500000</v>
+        <v>7590000</v>
       </c>
       <c r="C512">
-        <v>1500000</v>
+        <v>7590000</v>
       </c>
       <c r="D512">
         <v>0</v>
@@ -9793,10 +9793,10 @@
         <v>515</v>
       </c>
       <c r="B513">
-        <v>7590000</v>
+        <v>15960000</v>
       </c>
       <c r="C513">
-        <v>7590000</v>
+        <v>15960000</v>
       </c>
       <c r="D513">
         <v>0</v>
@@ -9807,10 +9807,10 @@
         <v>516</v>
       </c>
       <c r="B514">
-        <v>15960000</v>
+        <v>1250000</v>
       </c>
       <c r="C514">
-        <v>15960000</v>
+        <v>1250000</v>
       </c>
       <c r="D514">
         <v>0</v>
@@ -9821,10 +9821,10 @@
         <v>517</v>
       </c>
       <c r="B515">
-        <v>1250000</v>
+        <v>28000000</v>
       </c>
       <c r="C515">
-        <v>1250000</v>
+        <v>28000000</v>
       </c>
       <c r="D515">
         <v>0</v>
@@ -9835,10 +9835,10 @@
         <v>518</v>
       </c>
       <c r="B516">
-        <v>28000000</v>
+        <v>5800000</v>
       </c>
       <c r="C516">
-        <v>28000000</v>
+        <v>5800000</v>
       </c>
       <c r="D516">
         <v>0</v>
@@ -9849,10 +9849,10 @@
         <v>519</v>
       </c>
       <c r="B517">
-        <v>5800000</v>
+        <v>6490000</v>
       </c>
       <c r="C517">
-        <v>5800000</v>
+        <v>6490000</v>
       </c>
       <c r="D517">
         <v>0</v>
@@ -9863,10 +9863,10 @@
         <v>520</v>
       </c>
       <c r="B518">
-        <v>6490000</v>
+        <v>840000</v>
       </c>
       <c r="C518">
-        <v>6490000</v>
+        <v>840000</v>
       </c>
       <c r="D518">
         <v>0</v>
@@ -9877,10 +9877,10 @@
         <v>521</v>
       </c>
       <c r="B519">
-        <v>840000</v>
+        <v>5490000</v>
       </c>
       <c r="C519">
-        <v>840000</v>
+        <v>5490000</v>
       </c>
       <c r="D519">
         <v>0</v>
@@ -9891,10 +9891,10 @@
         <v>522</v>
       </c>
       <c r="B520">
-        <v>5490000</v>
+        <v>5700000</v>
       </c>
       <c r="C520">
-        <v>5490000</v>
+        <v>5700000</v>
       </c>
       <c r="D520">
         <v>0</v>
@@ -9905,10 +9905,10 @@
         <v>523</v>
       </c>
       <c r="B521">
-        <v>5700000</v>
+        <v>14440000</v>
       </c>
       <c r="C521">
-        <v>5700000</v>
+        <v>14440000</v>
       </c>
       <c r="D521">
         <v>0</v>
@@ -9919,10 +9919,10 @@
         <v>524</v>
       </c>
       <c r="B522">
-        <v>14440000</v>
+        <v>210000</v>
       </c>
       <c r="C522">
-        <v>14440000</v>
+        <v>210000</v>
       </c>
       <c r="D522">
         <v>0</v>
@@ -9933,10 +9933,10 @@
         <v>525</v>
       </c>
       <c r="B523">
-        <v>210000</v>
+        <v>30500000</v>
       </c>
       <c r="C523">
-        <v>210000</v>
+        <v>30500000</v>
       </c>
       <c r="D523">
         <v>0</v>
@@ -9947,10 +9947,10 @@
         <v>526</v>
       </c>
       <c r="B524">
-        <v>30500000</v>
+        <v>24110000</v>
       </c>
       <c r="C524">
-        <v>30500000</v>
+        <v>24110000</v>
       </c>
       <c r="D524">
         <v>0</v>
@@ -9961,10 +9961,10 @@
         <v>527</v>
       </c>
       <c r="B525">
-        <v>24110000</v>
+        <v>20030000</v>
       </c>
       <c r="C525">
-        <v>24110000</v>
+        <v>20030000</v>
       </c>
       <c r="D525">
         <v>0</v>
@@ -9975,13 +9975,13 @@
         <v>528</v>
       </c>
       <c r="B526">
-        <v>20030000</v>
+        <v>6387173464</v>
       </c>
       <c r="C526">
-        <v>20030000</v>
+        <v>1210309689</v>
       </c>
       <c r="D526">
-        <v>0</v>
+        <v>5176863775</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -11755,7 +11755,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -12200,10 +12200,10 @@
         <v>171990003</v>
       </c>
       <c r="C32">
-        <v>5100000000</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>-4928009997</v>
+        <v>171990003</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -12256,10 +12256,10 @@
         <v>2966830597</v>
       </c>
       <c r="C36">
-        <v>2967905000</v>
+        <v>2891041225</v>
       </c>
       <c r="D36">
-        <v>-1074403</v>
+        <v>75789372</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -12270,10 +12270,10 @@
         <v>363511995</v>
       </c>
       <c r="C37">
-        <v>500000000</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>-136488005</v>
+        <v>363511995</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -13012,10 +13012,10 @@
         <v>673086051</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>500000000</v>
       </c>
       <c r="D90">
-        <v>673086051</v>
+        <v>173086051</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -13244,43 +13244,57 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>754</v>
+        <v>528</v>
       </c>
       <c r="B107">
-        <v>26196143</v>
+        <v>6387173469</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>6387173469</v>
       </c>
       <c r="D107">
-        <v>26196143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B108">
-        <v>4235000</v>
+        <v>26196143</v>
       </c>
       <c r="C108">
         <v>0</v>
       </c>
       <c r="D108">
-        <v>4235000</v>
+        <v>26196143</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
+        <v>755</v>
+      </c>
+      <c r="B109">
+        <v>4235000</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>4235000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" t="s">
         <v>756</v>
       </c>
-      <c r="B109">
+      <c r="B110">
         <v>2713000</v>
       </c>
-      <c r="C109">
-        <v>0</v>
-      </c>
-      <c r="D109">
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
         <v>2713000</v>
       </c>
     </row>

--- a/docs/huyvu/sosach/nam2023/BAO_CAO_CONG_NO_2023.xlsx
+++ b/docs/huyvu/sosach/nam2023/BAO_CAO_CONG_NO_2023.xlsx
@@ -26,7 +26,7 @@
     <t>ĐÃ THU</t>
   </si>
   <si>
-    <t>DƯ CUỐI KỲ</t>
+    <t>BIẾN ĐỘNG</t>
   </si>
   <si>
     <t>AGRIBANK  CHI NHÁNH THÀNH PHỐ PLEIKU GIA LAI</t>
@@ -1985,7 +1985,7 @@
     <t>MUA VÀO</t>
   </si>
   <si>
-    <t>ĐÃ TRẢ</t>
+    <t>ĐÀ TRẢ</t>
   </si>
   <si>
     <t>CHI NHÁNH CÔNG TY CỔ PHẦN HUETRONICS (TỈNH THỪA THIÊN HUẾ)</t>
@@ -9975,13 +9975,13 @@
         <v>528</v>
       </c>
       <c r="B526">
-        <v>6387173464</v>
+        <v>0</v>
       </c>
       <c r="C526">
         <v>1210309689</v>
       </c>
       <c r="D526">
-        <v>5176863775</v>
+        <v>-1210309689</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -12256,10 +12256,10 @@
         <v>2966830597</v>
       </c>
       <c r="C36">
-        <v>2891041225</v>
+        <v>2437905000</v>
       </c>
       <c r="D36">
-        <v>75789372</v>
+        <v>528925597</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -13247,13 +13247,13 @@
         <v>528</v>
       </c>
       <c r="B107">
-        <v>6387173469</v>
+        <v>0</v>
       </c>
       <c r="C107">
-        <v>6387173469</v>
+        <v>6840309694</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>-6840309694</v>
       </c>
     </row>
     <row r="108" spans="1:4">
